--- a/public/templates/knowledge.xlsx
+++ b/public/templates/knowledge.xlsx
@@ -398,10 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A21"/>
-  <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:A23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,47 +482,58 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>9. 「适用学部」选择：all（全学部）、primary（小学部）、junior（初中部）、senior（高中部）、</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例</v>
+        <v xml:space="preserve">   repeat（复读部）；不填默认为 all（全学部），即所有学段可见。</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>| 文档标题 | 所属模块 | 来源类型 | 标签关键词 | 文档内容 | 来源出处 |</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>| 认知行为疗法概述 | self_growth | markdown | 认知行为,CBT,心理干预 | # 认知行为疗法... | 《心理咨询与治疗》第3版 |</v>
+        <v>示例</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>| 班级凝聚力建设方案 | class_system | markdown | 班级管理,凝聚力,团队建设 | ## 建设目标... | 教育部班级管理指南 |</v>
+        <v>| 文档标题 | 所属模块 | 来源类型 | 标签关键词 | 适用学部 | 文档内容 | 来源出处 |</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>| 认知行为疗法概述 | self_growth | markdown | 认知行为,CBT,心理干预 | all | # 认知行为疗法... | 《心理咨询与治疗》第3版 |</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>| 班级凝聚力建设方案 | class_system | markdown | 班级管理,凝聚力,团队建设 | all | ## 建设目标... | 教育部班级管理指南 |</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="61.6640625" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,12 +550,15 @@
         <v>标签关键词</v>
       </c>
       <c r="E1" t="str">
+        <v>适用学部</v>
+      </c>
+      <c r="F1" t="str">
         <v>文档内容*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>来源出处</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>备注</v>
       </c>
     </row>
@@ -564,7 +575,10 @@
       <c r="D2" t="str">
         <v>认知行为,CBT,心理干预</v>
       </c>
-      <c r="E2" t="str" xml:space="preserve">
+      <c r="E2" t="str">
+        <v>all</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve"># 认知行为疗法（CBT）概述
 ## 定义
 认知行为疗法是一种结构化、短程、着眼于当下的心理治疗方法...
@@ -573,10 +587,10 @@
 2. 改变这些思维模式可以缓解症状
 3. 通过练习可以习得新的应对方式</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>《心理咨询与治疗》第3版</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v/>
       </c>
     </row>
@@ -593,7 +607,10 @@
       <c r="D3" t="str">
         <v>班级管理,凝聚力,团队建设</v>
       </c>
-      <c r="E3" t="str" xml:space="preserve">
+      <c r="E3" t="str">
+        <v>all</v>
+      </c>
+      <c r="F3" t="str" xml:space="preserve">
         <v xml:space="preserve">## 建设目标
 提升班级成员间的信任感、归属感和协作能力。
 ## 实施步骤
@@ -604,10 +621,10 @@
 - 班级目标共商
 - 角色分工与轮换</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>教育部班级管理指南</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
@@ -624,7 +641,10 @@
       <c r="D4" t="str">
         <v>考试焦虑,情绪管理,放松训练</v>
       </c>
-      <c r="E4" t="str" xml:space="preserve">
+      <c r="E4" t="str">
+        <v>all</v>
+      </c>
+      <c r="F4" t="str" xml:space="preserve">
         <v xml:space="preserve">## 识别考试焦虑
 ### 常见表现
 - 生理：心跳加速、出汗、失眠
@@ -636,16 +656,16 @@
 2. 呼吸放松训练
 3. 积极自我暗示练习</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>《学校心理健康教育》</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>适用于初高中段</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/knowledge.xlsx
+++ b/public/templates/knowledge.xlsx
@@ -447,7 +447,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">   home_school（家校沟通）、student_case（学生个案）、learning_problem（学习问题）。</v>
+        <v xml:space="preserve">   home_school（家校沟通）、student_case（学生个案）、learning_problem（学习问题）、moral_education（德育）。</v>
       </c>
     </row>
     <row r="11">
